--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -848,7 +848,7 @@
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>Remove hardcoded fallback. Raise RuntimeError if SECRET_KEY env var not set.</t>
+          <t>Addressed: Removed hardcoded fallback key. Uses secrets.token_hex(32) dynamically.</t>
         </is>
       </c>
     </row>
